--- a/Dishwasher/Grading/1 stage/3-examples/Dishwasher_Grading_1-stage_2026-02-28_3-examples_CombinedHumanGradingVsClaude4.5SonnetAutoGrading_Claude4.5SonnetGeneration.xlsx
+++ b/Dishwasher/Grading/1 stage/3-examples/Dishwasher_Grading_1-stage_2026-02-28_3-examples_CombinedHumanGradingVsClaude4.5SonnetAutoGrading_Claude4.5SonnetGeneration.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marc-antoinenadeau/Desktop/Evaluations 2/Dishwasher/Grading/1 stage/2026-02-28/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marc-antoinenadeau/Desktop/B.Eng Software Engineering /7th Semester/Capstone/Code/Evaluations/Dishwasher/Grading/1 stage/3-examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56A65220-5340-5A43-946D-12204542A470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98617B4A-452A-8043-90DA-0B87B371CE45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17480" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dishwasher" sheetId="1" r:id="rId1"/>
@@ -651,7 +651,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -923,11 +923,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1076,19 +1085,28 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1366,10 +1384,18 @@
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Table_6" displayName="Table_6" ref="A1:D55">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Type"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Element"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Human"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="LLM"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Type">
+      <calculatedColumnFormula>'Human Grading'!A2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Element">
+      <calculatedColumnFormula>'Human Grading'!B2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Human">
+      <calculatedColumnFormula>'Human Grading'!C2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="LLM">
+      <calculatedColumnFormula>'LLM Grading'!C2</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="Inter-rater-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1381,7 +1407,9 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Type"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Element"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Human"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="LLM"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="LLM">
+      <calculatedColumnFormula>'LLM Grading'!C2</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="Weighted Cohens Kappa-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -15703,16 +15731,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="63" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
       <c r="J1" s="18" t="s">
         <v>108</v>
       </c>
@@ -16019,16 +16047,16 @@
     </row>
     <row r="11" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="12" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="60" t="s">
+      <c r="A12" s="63" t="s">
         <v>159</v>
       </c>
-      <c r="B12" s="61"/>
-      <c r="C12" s="61"/>
-      <c r="D12" s="61"/>
-      <c r="E12" s="61"/>
-      <c r="F12" s="61"/>
-      <c r="G12" s="61"/>
-      <c r="H12" s="61"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="19" t="s">
@@ -17340,30 +17368,30 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="66" t="s">
+      <c r="C1" s="60" t="s">
         <v>157</v>
       </c>
-      <c r="D1" s="66" t="s">
+      <c r="D1" s="60" t="s">
         <v>158</v>
       </c>
       <c r="E1" s="28"/>
-      <c r="F1" s="62" t="s">
+      <c r="F1" s="61" t="s">
         <v>121</v>
       </c>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
-      <c r="L1" s="64" t="s">
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="L1" s="65" t="s">
         <v>122</v>
       </c>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="63"/>
-      <c r="R1" s="63"/>
-      <c r="S1" s="63"/>
-      <c r="T1" s="63"/>
-      <c r="U1" s="63"/>
+      <c r="M1" s="66"/>
+      <c r="N1" s="66"/>
+      <c r="P1" s="61"/>
+      <c r="Q1" s="62"/>
+      <c r="R1" s="62"/>
+      <c r="S1" s="62"/>
+      <c r="T1" s="62"/>
+      <c r="U1" s="62"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="str">
@@ -17443,7 +17471,7 @@
       </c>
       <c r="H3" s="36">
         <f>COUNTIFS($C$2:$C$48, $F3, $D$2:$D$48, H$2)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3" s="37">
         <f>COUNTIFS($C$2:$C$48, $F3, $D$2:$D$48, I$2)+MAX(D49-C49,0)+MAX(D50-C50,0)+MAX(D51-C51,0)+MAX(D52-C52,0)+MAX(D53-C53,0)+MAX(D54-C54,0)+MAX(D55-C55,0)</f>
@@ -17451,7 +17479,7 @@
       </c>
       <c r="J3" s="2">
         <f t="shared" ref="J3:J5" si="0">SUM(G3:I3)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="38" t="s">
@@ -17494,15 +17522,15 @@
         <v>0.5</v>
       </c>
       <c r="G4" s="39">
-        <f t="shared" ref="G4:I4" si="1">COUNTIFS($C$2:$C$48, $F4, $D$2:$D$48, G$2)</f>
+        <f>COUNTIFS($C$2:$C$48, $F4, $D$2:$D$48, G$2)</f>
         <v>4</v>
       </c>
       <c r="H4" s="2">
-        <f t="shared" si="1"/>
+        <f>COUNTIFS($C$2:$C$48, $F4, $D$2:$D$48, H$2)</f>
         <v>2</v>
       </c>
       <c r="I4" s="40">
-        <f t="shared" si="1"/>
+        <f>COUNTIFS($C$2:$C$48, $F4, $D$2:$D$48, I$2)</f>
         <v>0</v>
       </c>
       <c r="J4" s="2">
@@ -17515,7 +17543,7 @@
       </c>
       <c r="M4" s="39">
         <f t="array" ref="M4">SUMPRODUCT(J3:J5/COUNTA($C$2:$C$102), TRANSPOSE(G6:I6)/COUNTA($C$2:$C$102))</f>
-        <v>0.38648834019204387</v>
+        <v>0.39506172839506171</v>
       </c>
       <c r="N4" s="40" t="s">
         <v>134</v>
@@ -17571,7 +17599,7 @@
       </c>
       <c r="M5" s="41">
         <f>(M3-M4)/(1-M4)</f>
-        <v>0.42649524874231409</v>
+        <v>0.41836734693877553</v>
       </c>
       <c r="N5" s="43" t="s">
         <v>135</v>
@@ -17606,15 +17634,15 @@
         <v>136</v>
       </c>
       <c r="G6" s="2">
-        <f t="shared" ref="G6:I6" si="2">SUM(G3:G5)</f>
+        <f t="shared" ref="G6:I6" si="1">SUM(G3:G5)</f>
         <v>19</v>
       </c>
       <c r="H6" s="2">
-        <f t="shared" si="2"/>
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="I6" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>27</v>
       </c>
       <c r="J6" s="2"/>
@@ -17675,17 +17703,17 @@
         <v>0</v>
       </c>
       <c r="E8" s="28"/>
-      <c r="F8" s="62" t="s">
+      <c r="F8" s="61" t="s">
         <v>137</v>
       </c>
-      <c r="G8" s="63"/>
-      <c r="H8" s="63"/>
-      <c r="I8" s="63"/>
-      <c r="L8" s="64" t="s">
+      <c r="G8" s="62"/>
+      <c r="H8" s="62"/>
+      <c r="I8" s="62"/>
+      <c r="L8" s="65" t="s">
         <v>138</v>
       </c>
-      <c r="M8" s="65"/>
-      <c r="N8" s="65"/>
+      <c r="M8" s="66"/>
+      <c r="N8" s="66"/>
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
@@ -17760,11 +17788,11 @@
         <v>0</v>
       </c>
       <c r="G10" s="35">
-        <f t="shared" ref="G10:H10" si="3">COUNTIFS($A$2:$A$92,$F$9,$C$2:$C$92,$F10,$D$2:$D$92,G$9)</f>
+        <f>COUNTIFS($A$2:$A$92,$F$9,$C$2:$C$92,$F10,$D$2:$D$92,G$9)</f>
         <v>1</v>
       </c>
       <c r="H10" s="36">
-        <f t="shared" si="3"/>
+        <f>COUNTIFS($A$2:$A$92,$F$9,$C$2:$C$92,$F10,$D$2:$D$92,H$9)</f>
         <v>0</v>
       </c>
       <c r="I10" s="37">
@@ -17772,7 +17800,7 @@
         <v>2</v>
       </c>
       <c r="J10" s="2">
-        <f t="shared" ref="J10:J12" si="4">SUM(G10:I10)</f>
+        <f t="shared" ref="J10:J12" si="2">SUM(G10:I10)</f>
         <v>3</v>
       </c>
       <c r="K10" s="2"/>
@@ -17809,19 +17837,19 @@
         <v>0.5</v>
       </c>
       <c r="G11" s="39">
-        <f t="shared" ref="G11:I11" si="5">COUNTIFS($A$2:$A$92,$F$9,$C$2:$C$92,$F11,$D$2:$D$92,G$9)</f>
+        <f>COUNTIFS($A$2:$A$92,$F$9,$C$2:$C$92,$F11,$D$2:$D$92,G$9)</f>
         <v>2</v>
       </c>
       <c r="H11" s="2">
-        <f t="shared" si="5"/>
+        <f>COUNTIFS($A$2:$A$92,$F$9,$C$2:$C$92,$F11,$D$2:$D$92,H$9)</f>
         <v>0</v>
       </c>
       <c r="I11" s="40">
-        <f t="shared" si="5"/>
+        <f>COUNTIFS($A$2:$A$92,$F$9,$C$2:$C$92,$F11,$D$2:$D$92,I$9)</f>
         <v>0</v>
       </c>
       <c r="J11" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="K11" s="2"/>
@@ -17870,7 +17898,7 @@
         <v>6</v>
       </c>
       <c r="J12" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="K12" s="2"/>
@@ -17907,15 +17935,15 @@
         <v>136</v>
       </c>
       <c r="G13" s="2">
-        <f t="shared" ref="G13:I13" si="6">SUM(G10:G12)</f>
+        <f t="shared" ref="G13:I13" si="3">SUM(G10:G12)</f>
         <v>4</v>
       </c>
       <c r="H13" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I13" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="J13" s="2"/>
@@ -17959,17 +17987,17 @@
         <v>1</v>
       </c>
       <c r="E15" s="28"/>
-      <c r="F15" s="62" t="s">
+      <c r="F15" s="61" t="s">
         <v>139</v>
       </c>
-      <c r="G15" s="63"/>
-      <c r="H15" s="63"/>
-      <c r="I15" s="63"/>
-      <c r="L15" s="64" t="s">
+      <c r="G15" s="62"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="62"/>
+      <c r="L15" s="65" t="s">
         <v>140</v>
       </c>
-      <c r="M15" s="65"/>
-      <c r="N15" s="65"/>
+      <c r="M15" s="66"/>
+      <c r="N15" s="66"/>
     </row>
     <row r="16" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="3" t="str">
@@ -18037,20 +18065,20 @@
         <v>0</v>
       </c>
       <c r="G17" s="35">
-        <f t="shared" ref="G17:H17" si="7">COUNTIFS($A$2:$A$92,$F$16,$C$2:$C$92,$F17,$D$2:$D$92,G$16)</f>
+        <f>COUNTIFS($A$2:$A$92,$F$16,$C$2:$C$92,$F17,$D$2:$D$92,G$16)</f>
         <v>3</v>
       </c>
       <c r="H17" s="36">
-        <f t="shared" si="7"/>
-        <v>2</v>
+        <f>COUNTIFS($A$2:$A$92,$F$16,$C$2:$C$92,$F17,$D$2:$D$92,H$16)</f>
+        <v>3</v>
       </c>
       <c r="I17" s="37">
         <f>COUNTIFS($A$2:$A$48,$F$16,$C$2:$C$48,$F17,$D$2:$D$48,I$16) + MAX(D50-C50,0)</f>
         <v>2</v>
       </c>
       <c r="J17" s="2">
-        <f t="shared" ref="J17:J19" si="8">SUM(G17:I17)</f>
-        <v>7</v>
+        <f t="shared" ref="J17:J19" si="4">SUM(G17:I17)</f>
+        <v>8</v>
       </c>
       <c r="K17" s="2"/>
       <c r="L17" s="38" t="s">
@@ -18086,19 +18114,19 @@
         <v>0.5</v>
       </c>
       <c r="G18" s="39">
-        <f t="shared" ref="G18:I18" si="9">COUNTIFS($A$2:$A$92,$F$16,$C$2:$C$92,$F18,$D$2:$D$92,G$16)</f>
+        <f>COUNTIFS($A$2:$A$92,$F$16,$C$2:$C$92,$F18,$D$2:$D$92,G$16)</f>
         <v>1</v>
       </c>
       <c r="H18" s="2">
-        <f t="shared" si="9"/>
+        <f>COUNTIFS($A$2:$A$92,$F$16,$C$2:$C$92,$F18,$D$2:$D$92,H$16)</f>
         <v>2</v>
       </c>
       <c r="I18" s="40">
-        <f t="shared" si="9"/>
+        <f>COUNTIFS($A$2:$A$92,$F$16,$C$2:$C$92,$F18,$D$2:$D$92,I$16)</f>
         <v>0</v>
       </c>
       <c r="J18" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="K18" s="2"/>
@@ -18107,7 +18135,7 @@
       </c>
       <c r="M18" s="39">
         <f t="array" ref="M18">SUMPRODUCT(J17:J19/COUNTIF($A$2:$A$102,F16), TRANSPOSE(G20:I20)/COUNTIF($A$2:$A$102,F16))</f>
-        <v>0.34750000000000003</v>
+        <v>0.36500000000000005</v>
       </c>
       <c r="N18" s="40" t="s">
         <v>134</v>
@@ -18147,7 +18175,7 @@
         <v>9</v>
       </c>
       <c r="J19" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="K19" s="2"/>
@@ -18156,7 +18184,7 @@
       </c>
       <c r="M19" s="41">
         <f>(M17-M18)/(1-M18)</f>
-        <v>0.54022988505747116</v>
+        <v>0.52755905511811008</v>
       </c>
       <c r="N19" s="43" t="s">
         <v>135</v>
@@ -18184,15 +18212,15 @@
         <v>136</v>
       </c>
       <c r="G20" s="2">
-        <f t="shared" ref="G20:I20" si="10">SUM(G17:G19)</f>
+        <f t="shared" ref="G20:I20" si="5">SUM(G17:G19)</f>
         <v>4</v>
       </c>
       <c r="H20" s="2">
-        <f t="shared" si="10"/>
-        <v>4</v>
+        <f t="shared" si="5"/>
+        <v>5</v>
       </c>
       <c r="I20" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="J20" s="2"/>
@@ -18236,17 +18264,17 @@
         <v>0</v>
       </c>
       <c r="E22" s="28"/>
-      <c r="F22" s="62" t="s">
+      <c r="F22" s="61" t="s">
         <v>141</v>
       </c>
-      <c r="G22" s="63"/>
-      <c r="H22" s="63"/>
-      <c r="I22" s="63"/>
-      <c r="L22" s="64" t="s">
+      <c r="G22" s="62"/>
+      <c r="H22" s="62"/>
+      <c r="I22" s="62"/>
+      <c r="L22" s="65" t="s">
         <v>142</v>
       </c>
-      <c r="M22" s="65"/>
-      <c r="N22" s="65"/>
+      <c r="M22" s="66"/>
+      <c r="N22" s="66"/>
     </row>
     <row r="23" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="3" t="str">
@@ -18314,11 +18342,11 @@
         <v>0</v>
       </c>
       <c r="G24" s="35">
-        <f t="shared" ref="G24:H24" si="11">COUNTIFS($A$2:$A$92,$F$23,$C$2:$C$92,$F24,$D$2:$D$92,G$23)</f>
+        <f>COUNTIFS($A$2:$A$92,$F$23,$C$2:$C$92,$F24,$D$2:$D$92,G$23)</f>
         <v>1</v>
       </c>
       <c r="H24" s="36">
-        <f t="shared" si="11"/>
+        <f>COUNTIFS($A$2:$A$92,$F$23,$C$2:$C$92,$F24,$D$2:$D$92,H$23)</f>
         <v>0</v>
       </c>
       <c r="I24" s="37">
@@ -18326,7 +18354,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="2">
-        <f t="shared" ref="J24:J26" si="12">SUM(G24:I24)</f>
+        <f t="shared" ref="J24:J26" si="6">SUM(G24:I24)</f>
         <v>1</v>
       </c>
       <c r="K24" s="2"/>
@@ -18363,19 +18391,19 @@
         <v>0.5</v>
       </c>
       <c r="G25" s="39">
-        <f t="shared" ref="G25:I25" si="13">COUNTIFS($A$2:$A$92,$F$23,$C$2:$C$92,$F25,$D$2:$D$92,G$23)</f>
+        <f>COUNTIFS($A$2:$A$92,$F$23,$C$2:$C$92,$F25,$D$2:$D$92,G$23)</f>
         <v>0</v>
       </c>
       <c r="H25" s="2">
-        <f t="shared" si="13"/>
+        <f>COUNTIFS($A$2:$A$92,$F$23,$C$2:$C$92,$F25,$D$2:$D$92,H$23)</f>
         <v>0</v>
       </c>
       <c r="I25" s="40">
-        <f t="shared" si="13"/>
+        <f>COUNTIFS($A$2:$A$92,$F$23,$C$2:$C$92,$F25,$D$2:$D$92,I$23)</f>
         <v>0</v>
       </c>
       <c r="J25" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K25" s="2"/>
@@ -18424,7 +18452,7 @@
         <v>1</v>
       </c>
       <c r="J26" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="K26" s="2"/>
@@ -18461,15 +18489,15 @@
         <v>136</v>
       </c>
       <c r="G27" s="2">
-        <f t="shared" ref="G27:I27" si="14">SUM(G24:G26)</f>
+        <f t="shared" ref="G27:I27" si="7">SUM(G24:G26)</f>
         <v>2</v>
       </c>
       <c r="H27" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I27" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="J27" s="2"/>
@@ -18513,17 +18541,17 @@
         <v>1</v>
       </c>
       <c r="E29" s="28"/>
-      <c r="F29" s="62" t="s">
+      <c r="F29" s="61" t="s">
         <v>143</v>
       </c>
-      <c r="G29" s="63"/>
-      <c r="H29" s="63"/>
-      <c r="I29" s="63"/>
-      <c r="L29" s="64" t="s">
+      <c r="G29" s="62"/>
+      <c r="H29" s="62"/>
+      <c r="I29" s="62"/>
+      <c r="L29" s="65" t="s">
         <v>144</v>
       </c>
-      <c r="M29" s="65"/>
-      <c r="N29" s="65"/>
+      <c r="M29" s="66"/>
+      <c r="N29" s="66"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="3" t="str">
@@ -18591,11 +18619,11 @@
         <v>0</v>
       </c>
       <c r="G31" s="35">
-        <f t="shared" ref="G31:H31" si="15">COUNTIFS($A$2:$A$92,$F$30,$C$2:$C$92,$F31,$D$2:$D$92,G$30)</f>
+        <f>COUNTIFS($A$2:$A$92,$F$30,$C$2:$C$92,$F31,$D$2:$D$92,G$30)</f>
         <v>3</v>
       </c>
       <c r="H31" s="36">
-        <f t="shared" si="15"/>
+        <f>COUNTIFS($A$2:$A$92,$F$30,$C$2:$C$92,$F31,$D$2:$D$92,H$30)</f>
         <v>0</v>
       </c>
       <c r="I31" s="37">
@@ -18603,7 +18631,7 @@
         <v>1</v>
       </c>
       <c r="J31" s="2">
-        <f t="shared" ref="J31:J33" si="16">SUM(G31:I31)</f>
+        <f t="shared" ref="J31:J33" si="8">SUM(G31:I31)</f>
         <v>4</v>
       </c>
       <c r="K31" s="2"/>
@@ -18640,19 +18668,19 @@
         <v>0.5</v>
       </c>
       <c r="G32" s="39">
-        <f t="shared" ref="G32:I32" si="17">COUNTIFS($A$2:$A$92,$F$30,$C$2:$C$92,$F32,$D$2:$D$92,G$30)</f>
+        <f>COUNTIFS($A$2:$A$92,$F$30,$C$2:$C$92,$F32,$D$2:$D$92,G$30)</f>
         <v>0</v>
       </c>
       <c r="H32" s="2">
-        <f t="shared" si="17"/>
+        <f>COUNTIFS($A$2:$A$92,$F$30,$C$2:$C$92,$F32,$D$2:$D$92,H$30)</f>
         <v>0</v>
       </c>
       <c r="I32" s="40">
-        <f t="shared" si="17"/>
+        <f>COUNTIFS($A$2:$A$92,$F$30,$C$2:$C$92,$F32,$D$2:$D$92,I$30)</f>
         <v>0</v>
       </c>
       <c r="J32" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K32" s="2"/>
@@ -18667,7 +18695,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="str">
         <f>'Human Grading'!A33</f>
         <v>Action</v>
@@ -18701,7 +18729,7 @@
         <v>1</v>
       </c>
       <c r="J33" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="K33" s="2"/>
@@ -18738,15 +18766,15 @@
         <v>136</v>
       </c>
       <c r="G34" s="2">
-        <f t="shared" ref="G34:I34" si="18">SUM(G31:G33)</f>
+        <f t="shared" ref="G34:I34" si="9">SUM(G31:G33)</f>
         <v>3</v>
       </c>
       <c r="H34" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="I34" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="J34" s="2"/>
@@ -18772,7 +18800,7 @@
       </c>
       <c r="E35" s="28"/>
     </row>
-    <row r="36" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="str">
         <f>'Human Grading'!A36</f>
         <v>History State</v>
@@ -18790,19 +18818,19 @@
         <v>0</v>
       </c>
       <c r="E36" s="28"/>
-      <c r="F36" s="62" t="s">
+      <c r="F36" s="61" t="s">
         <v>145</v>
       </c>
-      <c r="G36" s="63"/>
-      <c r="H36" s="63"/>
-      <c r="I36" s="63"/>
-      <c r="L36" s="64" t="s">
+      <c r="G36" s="62"/>
+      <c r="H36" s="62"/>
+      <c r="I36" s="62"/>
+      <c r="L36" s="65" t="s">
         <v>146</v>
       </c>
-      <c r="M36" s="65"/>
-      <c r="N36" s="65"/>
-    </row>
-    <row r="37" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M36" s="66"/>
+      <c r="N36" s="66"/>
+    </row>
+    <row r="37" spans="1:14" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="str">
         <f>'Human Grading'!A37</f>
         <v>Transition</v>
@@ -18868,11 +18896,11 @@
         <v>0</v>
       </c>
       <c r="G38" s="35">
-        <f t="shared" ref="G38:H38" si="19">COUNTIFS($A$2:$A$92,$F$37,$C$2:$C$92,$F38,$D$2:$D$92,G$37)</f>
+        <f>COUNTIFS($A$2:$A$92,$F$37,$C$2:$C$92,$F38,$D$2:$D$92,G$37)</f>
         <v>2</v>
       </c>
       <c r="H38" s="36">
-        <f t="shared" si="19"/>
+        <f>COUNTIFS($A$2:$A$92,$F$37,$C$2:$C$92,$F38,$D$2:$D$92,H$37)</f>
         <v>1</v>
       </c>
       <c r="I38" s="37">
@@ -18880,7 +18908,7 @@
         <v>1</v>
       </c>
       <c r="J38" s="2">
-        <f t="shared" ref="J38:J40" si="20">SUM(G38:I38)</f>
+        <f t="shared" ref="J38:J40" si="10">SUM(G38:I38)</f>
         <v>4</v>
       </c>
       <c r="K38" s="2"/>
@@ -18917,19 +18945,19 @@
         <v>0.5</v>
       </c>
       <c r="G39" s="39">
-        <f t="shared" ref="G39:I39" si="21">COUNTIFS($A$2:$A$92,$F$37,$C$2:$C$92,$F39,$D$2:$D$92,G$37)</f>
+        <f>COUNTIFS($A$2:$A$92,$F$37,$C$2:$C$92,$F39,$D$2:$D$92,G$37)</f>
         <v>0</v>
       </c>
       <c r="H39" s="2">
-        <f t="shared" si="21"/>
+        <f>COUNTIFS($A$2:$A$92,$F$37,$C$2:$C$92,$F39,$D$2:$D$92,H$37)</f>
         <v>0</v>
       </c>
       <c r="I39" s="40">
-        <f t="shared" si="21"/>
+        <f>COUNTIFS($A$2:$A$92,$F$37,$C$2:$C$92,$F39,$D$2:$D$92,I$37)</f>
         <v>0</v>
       </c>
       <c r="J39" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K39" s="2"/>
@@ -18944,7 +18972,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="str">
         <f>'Human Grading'!A40</f>
         <v>Action</v>
@@ -18978,7 +19006,7 @@
         <v>2</v>
       </c>
       <c r="J40" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
       <c r="K40" s="2"/>
@@ -19015,15 +19043,15 @@
         <v>136</v>
       </c>
       <c r="G41" s="2">
-        <f t="shared" ref="G41:I41" si="22">SUM(G38:G40)</f>
+        <f t="shared" ref="G41:I41" si="11">SUM(G38:G40)</f>
         <v>2</v>
       </c>
       <c r="H41" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
       <c r="I41" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
       <c r="J41" s="2"/>
@@ -19049,7 +19077,7 @@
       </c>
       <c r="E42" s="28"/>
     </row>
-    <row r="43" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="str">
         <f>'Human Grading'!A43</f>
         <v>Transition</v>
@@ -19067,19 +19095,19 @@
         <v>1</v>
       </c>
       <c r="E43" s="28"/>
-      <c r="F43" s="62" t="s">
+      <c r="F43" s="61" t="s">
         <v>147</v>
       </c>
-      <c r="G43" s="63"/>
-      <c r="H43" s="63"/>
-      <c r="I43" s="63"/>
-      <c r="L43" s="64" t="s">
+      <c r="G43" s="62"/>
+      <c r="H43" s="62"/>
+      <c r="I43" s="62"/>
+      <c r="L43" s="65" t="s">
         <v>148</v>
       </c>
-      <c r="M43" s="65"/>
-      <c r="N43" s="65"/>
-    </row>
-    <row r="44" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M43" s="66"/>
+      <c r="N43" s="66"/>
+    </row>
+    <row r="44" spans="1:14" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="str">
         <f>'Human Grading'!A44</f>
         <v>Action</v>
@@ -19145,11 +19173,11 @@
         <v>0</v>
       </c>
       <c r="G45" s="35">
-        <f t="shared" ref="G45:H45" si="23">COUNTIFS($A$2:$A$92,$F$44,$C$2:$C$92,$F45,$D$2:$D$92,G$44)</f>
+        <f>COUNTIFS($A$2:$A$92,$F$44,$C$2:$C$92,$F45,$D$2:$D$92,G$44)</f>
         <v>1</v>
       </c>
       <c r="H45" s="36">
-        <f t="shared" si="23"/>
+        <f>COUNTIFS($A$2:$A$92,$F$44,$C$2:$C$92,$F45,$D$2:$D$92,H$44)</f>
         <v>0</v>
       </c>
       <c r="I45" s="37">
@@ -19157,7 +19185,7 @@
         <v>1</v>
       </c>
       <c r="J45" s="2">
-        <f t="shared" ref="J45:J47" si="24">SUM(G45:I45)</f>
+        <f t="shared" ref="J45:J47" si="12">SUM(G45:I45)</f>
         <v>2</v>
       </c>
       <c r="K45" s="2"/>
@@ -19194,19 +19222,19 @@
         <v>0.5</v>
       </c>
       <c r="G46" s="39">
-        <f t="shared" ref="G46:I46" si="25">COUNTIFS($A$2:$A$92,$F$44,$C$2:$C$92,$F46,$D$2:$D$92,G$44)</f>
+        <f>COUNTIFS($A$2:$A$92,$F$44,$C$2:$C$92,$F46,$D$2:$D$92,G$44)</f>
         <v>0</v>
       </c>
       <c r="H46" s="2">
-        <f t="shared" si="25"/>
+        <f>COUNTIFS($A$2:$A$92,$F$44,$C$2:$C$92,$F46,$D$2:$D$92,H$44)</f>
         <v>0</v>
       </c>
       <c r="I46" s="40">
-        <f t="shared" si="25"/>
+        <f>COUNTIFS($A$2:$A$92,$F$44,$C$2:$C$92,$F46,$D$2:$D$92,I$44)</f>
         <v>0</v>
       </c>
       <c r="J46" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K46" s="2"/>
@@ -19221,7 +19249,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="47" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="str">
         <f>'Human Grading'!A47</f>
         <v>Transition</v>
@@ -19234,9 +19262,9 @@
         <f>'Human Grading'!C47</f>
         <v>0</v>
       </c>
-      <c r="D47" s="11" t="str">
-        <f>'LLM Grading'!D42</f>
-        <v>dryingComplete transition from DryingActive to Idle represents completion</v>
+      <c r="D47" s="11">
+        <f>'LLM Grading'!C47</f>
+        <v>0.5</v>
       </c>
       <c r="E47" s="28"/>
       <c r="F47" s="34">
@@ -19255,7 +19283,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K47" s="2"/>
@@ -19271,19 +19299,19 @@
       </c>
     </row>
     <row r="48" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A48" s="6" t="str">
+      <c r="A48" s="68" t="str">
         <f>'Human Grading'!A48</f>
         <v>Transition</v>
       </c>
-      <c r="B48" s="7" t="str">
+      <c r="B48" s="69" t="str">
         <f>'Human Grading'!B48</f>
         <v>after 5 min (Suspended ⇒ Idle)</v>
       </c>
-      <c r="C48" s="11">
+      <c r="C48" s="67">
         <f>'Human Grading'!C48</f>
         <v>1</v>
       </c>
-      <c r="D48" s="11">
+      <c r="D48" s="67">
         <f>'LLM Grading'!C48</f>
         <v>1</v>
       </c>
@@ -19292,15 +19320,15 @@
         <v>136</v>
       </c>
       <c r="G48" s="2">
-        <f t="shared" ref="G48:I48" si="26">SUM(G45:G47)</f>
+        <f t="shared" ref="G48:I48" si="13">SUM(G45:G47)</f>
         <v>1</v>
       </c>
       <c r="H48" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I48" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="J48" s="2"/>
@@ -19316,17 +19344,17 @@
         <f>'Human Grading'!B49</f>
         <v>additional elements</v>
       </c>
-      <c r="C49" s="48">
+      <c r="C49" s="11">
         <f>'Human Grading'!C49</f>
         <v>0</v>
       </c>
-      <c r="D49" s="48">
+      <c r="D49" s="11">
         <f>'LLM Grading'!C49</f>
         <v>1</v>
       </c>
       <c r="E49" s="28"/>
     </row>
-    <row r="50" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="str">
         <f>'Human Grading'!A50</f>
         <v>Transition</v>
@@ -19344,19 +19372,19 @@
         <v>1</v>
       </c>
       <c r="E50" s="28"/>
-      <c r="F50" s="62" t="s">
+      <c r="F50" s="61" t="s">
         <v>149</v>
       </c>
-      <c r="G50" s="63"/>
-      <c r="H50" s="63"/>
-      <c r="I50" s="63"/>
-      <c r="L50" s="64" t="s">
+      <c r="G50" s="62"/>
+      <c r="H50" s="62"/>
+      <c r="I50" s="62"/>
+      <c r="L50" s="65" t="s">
         <v>150</v>
       </c>
-      <c r="M50" s="65"/>
-      <c r="N50" s="65"/>
-    </row>
-    <row r="51" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M50" s="66"/>
+      <c r="N50" s="66"/>
+    </row>
+    <row r="51" spans="1:14" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="str">
         <f>'Human Grading'!A51</f>
         <v>Guard</v>
@@ -19422,11 +19450,11 @@
         <v>0</v>
       </c>
       <c r="G52" s="35">
-        <f t="shared" ref="G52:H52" si="27">COUNTIFS($A$2:$A$92,$F$51,$C$2:$C$92,$F52,$D$2:$D$92,G$51)</f>
+        <f>COUNTIFS($A$2:$A$92,$F$51,$C$2:$C$92,$F52,$D$2:$D$92,G$51)</f>
         <v>2</v>
       </c>
       <c r="H52" s="36">
-        <f t="shared" si="27"/>
+        <f>COUNTIFS($A$2:$A$92,$F$51,$C$2:$C$92,$F52,$D$2:$D$92,H$51)</f>
         <v>0</v>
       </c>
       <c r="I52" s="37">
@@ -19434,7 +19462,7 @@
         <v>0</v>
       </c>
       <c r="J52" s="2">
-        <f t="shared" ref="J52:J54" si="28">SUM(G52:I52)</f>
+        <f t="shared" ref="J52:J54" si="14">SUM(G52:I52)</f>
         <v>2</v>
       </c>
       <c r="K52" s="2"/>
@@ -19471,19 +19499,19 @@
         <v>0.5</v>
       </c>
       <c r="G53" s="39">
-        <f t="shared" ref="G53:I53" si="29">COUNTIFS($A$2:$A$92,$F$51,$C$2:$C$92,$F53,$D$2:$D$92,G$51)</f>
+        <f>COUNTIFS($A$2:$A$92,$F$51,$C$2:$C$92,$F53,$D$2:$D$92,G$51)</f>
         <v>1</v>
       </c>
       <c r="H53" s="2">
-        <f t="shared" si="29"/>
+        <f>COUNTIFS($A$2:$A$92,$F$51,$C$2:$C$92,$F53,$D$2:$D$92,H$51)</f>
         <v>0</v>
       </c>
       <c r="I53" s="40">
-        <f t="shared" si="29"/>
+        <f>COUNTIFS($A$2:$A$92,$F$51,$C$2:$C$92,$F53,$D$2:$D$92,I$51)</f>
         <v>0</v>
       </c>
       <c r="J53" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="K53" s="2"/>
@@ -19498,7 +19526,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="str">
         <f>'Human Grading'!A54</f>
         <v>Region</v>
@@ -19532,7 +19560,7 @@
         <v>0</v>
       </c>
       <c r="J54" s="2">
-        <f t="shared" si="28"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="K54" s="2"/>
@@ -19569,15 +19597,15 @@
         <v>136</v>
       </c>
       <c r="G55" s="2">
-        <f t="shared" ref="G55:I55" si="30">SUM(G52:G54)</f>
+        <f t="shared" ref="G55:I55" si="15">SUM(G52:G54)</f>
         <v>3</v>
       </c>
       <c r="H55" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="I55" s="2">
-        <f t="shared" si="30"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J55" s="2"/>
@@ -20738,25 +20766,25 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="66" t="s">
+      <c r="C1" s="60" t="s">
         <v>157</v>
       </c>
-      <c r="D1" s="66" t="s">
+      <c r="D1" s="60" t="s">
         <v>158</v>
       </c>
       <c r="E1" s="28"/>
-      <c r="F1" s="62" t="s">
+      <c r="F1" s="61" t="s">
         <v>121</v>
       </c>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
-      <c r="L1" s="62" t="s">
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="L1" s="61" t="s">
         <v>151</v>
       </c>
-      <c r="M1" s="63"/>
-      <c r="N1" s="63"/>
-      <c r="O1" s="63"/>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="62"/>
     </row>
     <row r="2" spans="1:24" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="str">
@@ -20855,7 +20883,7 @@
       </c>
       <c r="H3" s="36">
         <f>COUNTIFS($C$2:$C$48, $F3, $D$2:$D$48, H$2)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3" s="37">
         <f>COUNTIFS($C$2:$C$48, $F3, $D$2:$D$48, I$2)+MAX(D49-C49,0)+MAX(D50-C50,0)+MAX(D51-C51,0)+MAX(D52-C52,0)+MAX(D53-C53,0)+MAX(D54-C54,0)+MAX(D55-C55,0)</f>
@@ -20863,7 +20891,7 @@
       </c>
       <c r="J3" s="2">
         <f t="shared" ref="J3:J5" si="0">SUM(G3:I3)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="34">
@@ -20887,15 +20915,15 @@
       </c>
       <c r="R3" s="35">
         <f t="shared" ref="R3:T3" si="2">($J3/$J$6) * (G$6/$J$6)</f>
-        <v>0.15557137771448915</v>
+        <v>0.15637860082304525</v>
       </c>
       <c r="S3" s="36">
         <f t="shared" si="2"/>
-        <v>5.731577073691705E-2</v>
+        <v>6.5843621399176946E-2</v>
       </c>
       <c r="T3" s="37">
         <f t="shared" si="2"/>
-        <v>0.22107511569953719</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="U3" s="2"/>
       <c r="V3" s="38" t="s">
@@ -20903,7 +20931,7 @@
       </c>
       <c r="W3" s="35">
         <f>SUMPRODUCT(G3:I5, M3:O5) /$J$6</f>
-        <v>0.25471698113207547</v>
+        <v>0.25925925925925924</v>
       </c>
       <c r="X3" s="37" t="s">
         <v>153</v>
@@ -20968,15 +20996,15 @@
       </c>
       <c r="R4" s="39">
         <f t="shared" ref="R4:T4" si="5">($J4/$J$6) * (G$6/$J$6)</f>
-        <v>4.058383766464934E-2</v>
+        <v>3.9094650205761312E-2</v>
       </c>
       <c r="S4" s="2">
         <f t="shared" si="5"/>
-        <v>1.4951940192239232E-2</v>
+        <v>1.6460905349794237E-2</v>
       </c>
       <c r="T4" s="40">
         <f t="shared" si="5"/>
-        <v>5.7671769312922748E-2</v>
+        <v>5.5555555555555552E-2</v>
       </c>
       <c r="U4" s="2"/>
       <c r="V4" s="38" t="s">
@@ -20984,7 +21012,7 @@
       </c>
       <c r="W4" s="39">
         <f>SUMPRODUCT(R3:T5, M3:O5)</f>
-        <v>0.4911000355998576</v>
+        <v>0.49176954732510286</v>
       </c>
       <c r="X4" s="40" t="s">
         <v>155</v>
@@ -21049,15 +21077,15 @@
       </c>
       <c r="R5" s="41">
         <f t="shared" ref="R5:T5" si="7">($J5/$J$6) * (G$6/$J$6)</f>
-        <v>0.16233535065859736</v>
+        <v>0.15637860082304525</v>
       </c>
       <c r="S5" s="42">
         <f t="shared" si="7"/>
-        <v>5.9807760768956927E-2</v>
+        <v>6.5843621399176946E-2</v>
       </c>
       <c r="T5" s="43">
         <f t="shared" si="7"/>
-        <v>0.23068707725169099</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="U5" s="2"/>
       <c r="V5" s="38" t="s">
@@ -21065,7 +21093,7 @@
       </c>
       <c r="W5" s="41">
         <f>1-W3/W4</f>
-        <v>0.48133381660021746</v>
+        <v>0.47280334728033468</v>
       </c>
       <c r="X5" s="43" t="s">
         <v>156</v>
@@ -21098,7 +21126,7 @@
       </c>
       <c r="H6" s="2">
         <f t="shared" si="8"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I6" s="2">
         <f t="shared" si="8"/>
@@ -21106,7 +21134,7 @@
       </c>
       <c r="J6" s="2">
         <f>SUM(G3:I5)</f>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
@@ -21160,12 +21188,12 @@
         <v>0</v>
       </c>
       <c r="E8" s="28"/>
-      <c r="F8" s="62" t="s">
+      <c r="F8" s="61" t="s">
         <v>137</v>
       </c>
-      <c r="G8" s="63"/>
-      <c r="H8" s="63"/>
-      <c r="I8" s="63"/>
+      <c r="G8" s="62"/>
+      <c r="H8" s="62"/>
+      <c r="I8" s="62"/>
     </row>
     <row r="9" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="3" t="str">
@@ -21555,12 +21583,12 @@
         <v>1</v>
       </c>
       <c r="E15" s="28"/>
-      <c r="F15" s="62" t="s">
+      <c r="F15" s="61" t="s">
         <v>139</v>
       </c>
-      <c r="G15" s="63"/>
-      <c r="H15" s="63"/>
-      <c r="I15" s="63"/>
+      <c r="G15" s="62"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="62"/>
     </row>
     <row r="16" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="3" t="str">
@@ -21659,7 +21687,7 @@
       </c>
       <c r="H17" s="36">
         <f t="shared" si="19"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I17" s="37">
         <f>COUNTIFS($A$2:$A$48,$F$16,$C$2:$C$48,$F17,$D$2:$D$48,I$16) + MAX(D50-C50,0)</f>
@@ -21667,7 +21695,7 @@
       </c>
       <c r="J17" s="2">
         <f t="shared" ref="J17:J19" si="20">SUM(G17:I17)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K17" s="2"/>
       <c r="L17" s="34">
@@ -21691,15 +21719,15 @@
       </c>
       <c r="R17" s="35">
         <f t="shared" ref="R17:T17" si="22">($J17/$J$20) * (G$20/$J$20)</f>
-        <v>7.7562326869806089E-2</v>
+        <v>8.0000000000000016E-2</v>
       </c>
       <c r="S17" s="36">
         <f t="shared" si="22"/>
-        <v>7.7562326869806089E-2</v>
+        <v>0.1</v>
       </c>
       <c r="T17" s="37">
         <f t="shared" si="22"/>
-        <v>0.21329639889196675</v>
+        <v>0.22000000000000003</v>
       </c>
       <c r="U17" s="2"/>
       <c r="V17" s="38" t="s">
@@ -21707,7 +21735,7 @@
       </c>
       <c r="W17" s="35">
         <f>SUMPRODUCT(G17:I19, M17:O19) /$J$20</f>
-        <v>0.18421052631578946</v>
+        <v>0.2</v>
       </c>
       <c r="X17" s="37" t="s">
         <v>153</v>
@@ -21772,15 +21800,15 @@
       </c>
       <c r="R18" s="39">
         <f t="shared" ref="R18:T18" si="25">($J18/$J$20) * (G$20/$J$20)</f>
-        <v>3.3240997229916892E-2</v>
+        <v>0.03</v>
       </c>
       <c r="S18" s="2">
         <f t="shared" si="25"/>
-        <v>3.3240997229916892E-2</v>
+        <v>3.7499999999999999E-2</v>
       </c>
       <c r="T18" s="40">
         <f t="shared" si="25"/>
-        <v>9.141274238227147E-2</v>
+        <v>8.2500000000000004E-2</v>
       </c>
       <c r="U18" s="2"/>
       <c r="V18" s="38" t="s">
@@ -21788,7 +21816,7 @@
       </c>
       <c r="W18" s="39">
         <f>SUMPRODUCT(R17:T19, M17:O19)</f>
-        <v>0.46398891966759004</v>
+        <v>0.47250000000000009</v>
       </c>
       <c r="X18" s="40" t="s">
         <v>155</v>
@@ -21853,15 +21881,15 @@
       </c>
       <c r="R19" s="41">
         <f t="shared" ref="R19:T19" si="27">($J19/$J$20) * (G$20/$J$20)</f>
-        <v>9.9722991689750684E-2</v>
+        <v>9.0000000000000011E-2</v>
       </c>
       <c r="S19" s="42">
         <f t="shared" si="27"/>
-        <v>9.9722991689750684E-2</v>
+        <v>0.1125</v>
       </c>
       <c r="T19" s="43">
         <f t="shared" si="27"/>
-        <v>0.2742382271468144</v>
+        <v>0.24750000000000003</v>
       </c>
       <c r="U19" s="2"/>
       <c r="V19" s="38" t="s">
@@ -21869,7 +21897,7 @@
       </c>
       <c r="W19" s="41">
         <f>1-W17/W18</f>
-        <v>0.60298507462686568</v>
+        <v>0.57671957671957674</v>
       </c>
       <c r="X19" s="43" t="s">
         <v>156</v>
@@ -21902,7 +21930,7 @@
       </c>
       <c r="H20" s="2">
         <f t="shared" si="28"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I20" s="2">
         <f t="shared" si="28"/>
@@ -21910,7 +21938,7 @@
       </c>
       <c r="J20" s="2">
         <f>SUM(G17:I19)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -21950,12 +21978,12 @@
         <v>0</v>
       </c>
       <c r="E22" s="28"/>
-      <c r="F22" s="62" t="s">
+      <c r="F22" s="61" t="s">
         <v>141</v>
       </c>
-      <c r="G22" s="63"/>
-      <c r="H22" s="63"/>
-      <c r="I22" s="63"/>
+      <c r="G22" s="62"/>
+      <c r="H22" s="62"/>
+      <c r="I22" s="62"/>
     </row>
     <row r="23" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="3" t="str">
@@ -22345,12 +22373,12 @@
         <v>1</v>
       </c>
       <c r="E29" s="28"/>
-      <c r="F29" s="62" t="s">
+      <c r="F29" s="61" t="s">
         <v>143</v>
       </c>
-      <c r="G29" s="63"/>
-      <c r="H29" s="63"/>
-      <c r="I29" s="63"/>
+      <c r="G29" s="62"/>
+      <c r="H29" s="62"/>
+      <c r="I29" s="62"/>
     </row>
     <row r="30" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="3" t="str">
@@ -22740,12 +22768,12 @@
         <v>0</v>
       </c>
       <c r="E36" s="28"/>
-      <c r="F36" s="62" t="s">
+      <c r="F36" s="61" t="s">
         <v>145</v>
       </c>
-      <c r="G36" s="63"/>
-      <c r="H36" s="63"/>
-      <c r="I36" s="63"/>
+      <c r="G36" s="62"/>
+      <c r="H36" s="62"/>
+      <c r="I36" s="62"/>
     </row>
     <row r="37" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="3" t="str">
@@ -23135,12 +23163,12 @@
         <v>1</v>
       </c>
       <c r="E43" s="28"/>
-      <c r="F43" s="62" t="s">
+      <c r="F43" s="61" t="s">
         <v>147</v>
       </c>
-      <c r="G43" s="63"/>
-      <c r="H43" s="63"/>
-      <c r="I43" s="63"/>
+      <c r="G43" s="62"/>
+      <c r="H43" s="62"/>
+      <c r="I43" s="62"/>
     </row>
     <row r="44" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="3" t="str">
@@ -23387,9 +23415,9 @@
         <f>'Human Grading'!C47</f>
         <v>0</v>
       </c>
-      <c r="D47" s="11" t="str">
-        <f>'LLM Grading'!D42</f>
-        <v>dryingComplete transition from DryingActive to Idle represents completion</v>
+      <c r="D47" s="11">
+        <f>'LLM Grading'!C47</f>
+        <v>0.5</v>
       </c>
       <c r="E47" s="28"/>
       <c r="F47" s="34">
@@ -23468,7 +23496,7 @@
         <f>'Human Grading'!C48</f>
         <v>1</v>
       </c>
-      <c r="D48" s="11">
+      <c r="D48" s="67">
         <f>'LLM Grading'!C48</f>
         <v>1</v>
       </c>
@@ -23506,7 +23534,7 @@
         <f>'Human Grading'!C49</f>
         <v>0</v>
       </c>
-      <c r="D49" s="48">
+      <c r="D49" s="11">
         <f>'LLM Grading'!C49</f>
         <v>1</v>
       </c>
@@ -23530,12 +23558,12 @@
         <v>1</v>
       </c>
       <c r="E50" s="28"/>
-      <c r="F50" s="62" t="s">
+      <c r="F50" s="61" t="s">
         <v>149</v>
       </c>
-      <c r="G50" s="63"/>
-      <c r="H50" s="63"/>
-      <c r="I50" s="63"/>
+      <c r="G50" s="62"/>
+      <c r="H50" s="62"/>
+      <c r="I50" s="62"/>
     </row>
     <row r="51" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="3" t="str">
